--- a/SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_Benchmarking_100_APM_DF.xlsx
+++ b/SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_Benchmarking_100_APM_DF.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
   <si>
     <t>Run</t>
   </si>
@@ -33,16 +33,28 @@
     <t>Seed</t>
   </si>
   <si>
-    <t>PathfindingTime_s</t>
+    <t>InitialPathfindingTime_s</t>
+  </si>
+  <si>
+    <t>IncrementalPathfindingTime_s</t>
   </si>
   <si>
     <t>SimulationTime_s</t>
   </si>
   <si>
+    <t>Total TL</t>
+  </si>
+  <si>
     <t>Number of runs</t>
   </si>
   <si>
-    <t>Average pathfinding time (s)</t>
+    <t>Average initial pathfinding time (s)</t>
+  </si>
+  <si>
+    <t>Average incremental pathfinding time (s)</t>
+  </si>
+  <si>
+    <t>Average total pathfinding time (s)</t>
   </si>
   <si>
     <t>Average simulation time (s)</t>
@@ -397,10 +409,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,729 +425,1051 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1.0</v>
       </c>
       <c r="B2">
-        <v>3.401561005e9</v>
+        <v>2.937057374e9</v>
       </c>
       <c r="C2">
-        <v>539.9871195000001</v>
+        <v>37.5601391</v>
       </c>
       <c r="D2">
-        <v>1.566275100000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>426.5194939</v>
+      </c>
+      <c r="E2">
+        <v>1.3578049000000005</v>
+      </c>
+      <c r="F2">
+        <v>77.49000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2.0</v>
       </c>
       <c r="B3">
-        <v>2.034943597e9</v>
+        <v>2.800073396e9</v>
       </c>
       <c r="C3">
-        <v>542.0196066999999</v>
+        <v>37.5837901</v>
       </c>
       <c r="D3">
-        <v>0.11815869999999995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>415.6546551</v>
+      </c>
+      <c r="E3">
+        <v>0.11519569999999993</v>
+      </c>
+      <c r="F3">
+        <v>76.87500000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3.0</v>
       </c>
       <c r="B4">
-        <v>2.898463391e9</v>
+        <v>2.65025485e9</v>
       </c>
       <c r="C4">
-        <v>564.016623</v>
+        <v>37.252592199999995</v>
       </c>
       <c r="D4">
-        <v>0.12435779999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>415.8282618</v>
+      </c>
+      <c r="E4">
+        <v>0.12335670000000003</v>
+      </c>
+      <c r="F4">
+        <v>76.49500000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4.0</v>
       </c>
       <c r="B5">
-        <v>1.003689115e9</v>
+        <v>8.78248493e8</v>
       </c>
       <c r="C5">
-        <v>561.8937409</v>
+        <v>36.7125319</v>
       </c>
       <c r="D5">
-        <v>0.12931620000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>414.4074491</v>
+      </c>
+      <c r="E5">
+        <v>0.1101571</v>
+      </c>
+      <c r="F5">
+        <v>76.76500000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5.0</v>
       </c>
       <c r="B6">
-        <v>1.824949416e9</v>
+        <v>1.037833551e9</v>
       </c>
       <c r="C6">
-        <v>545.2834908</v>
+        <v>37.620900999999996</v>
       </c>
       <c r="D6">
-        <v>0.12744189999999989</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>415.0743129</v>
+      </c>
+      <c r="E6">
+        <v>0.10738789999999987</v>
+      </c>
+      <c r="F6">
+        <v>72.30000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6.0</v>
       </c>
       <c r="B7">
-        <v>2.853846265e9</v>
+        <v>3.010059209e9</v>
       </c>
       <c r="C7">
-        <v>559.9133889</v>
+        <v>37.6856837</v>
       </c>
       <c r="D7">
-        <v>0.18017190000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>426.1482258</v>
+      </c>
+      <c r="E7">
+        <v>0.1207922</v>
+      </c>
+      <c r="F7">
+        <v>75.10000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7.0</v>
       </c>
       <c r="B8">
-        <v>1.790088564e9</v>
+        <v>7.14527533e8</v>
       </c>
       <c r="C8">
-        <v>564.8074977</v>
+        <v>38.219024499999996</v>
       </c>
       <c r="D8">
-        <v>0.12309239999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>428.0923537</v>
+      </c>
+      <c r="E8">
+        <v>0.12165250000000015</v>
+      </c>
+      <c r="F8">
+        <v>77.85000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8.0</v>
       </c>
       <c r="B9">
-        <v>7.14127886e8</v>
+        <v>5.63148915e8</v>
       </c>
       <c r="C9">
-        <v>553.3847807</v>
+        <v>38.48588779999999</v>
       </c>
       <c r="D9">
-        <v>0.13144999999999987</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>428.45022359999996</v>
+      </c>
+      <c r="E9">
+        <v>0.11765789999999995</v>
+      </c>
+      <c r="F9">
+        <v>62.38500000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9.0</v>
       </c>
       <c r="B10">
-        <v>3.487516438e9</v>
+        <v>2.774923005e9</v>
       </c>
       <c r="C10">
-        <v>568.5981492</v>
+        <v>38.6141663</v>
       </c>
       <c r="D10">
-        <v>0.12061200000000011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>431.08913149999995</v>
+      </c>
+      <c r="E10">
+        <v>0.11008230000000002</v>
+      </c>
+      <c r="F10">
+        <v>69.92000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10.0</v>
       </c>
       <c r="B11">
-        <v>1.330624921e9</v>
+        <v>1.27156534e8</v>
       </c>
       <c r="C11">
-        <v>568.8013216</v>
+        <v>37.9323175</v>
       </c>
       <c r="D11">
-        <v>0.12705640000000012</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>429.8712306</v>
+      </c>
+      <c r="E11">
+        <v>0.11893669999999998</v>
+      </c>
+      <c r="F11">
+        <v>85.96500000000009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11.0</v>
       </c>
       <c r="B12">
-        <v>1.507181965e9</v>
+        <v>1.630567135e9</v>
       </c>
       <c r="C12">
-        <v>540.0602953</v>
+        <v>39.08059</v>
       </c>
       <c r="D12">
-        <v>0.11367000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>429.0715506</v>
+      </c>
+      <c r="E12">
+        <v>0.12859979999999993</v>
+      </c>
+      <c r="F12">
+        <v>70.82000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12.0</v>
       </c>
       <c r="B13">
-        <v>3.533386732e9</v>
+        <v>4.50627969e8</v>
       </c>
       <c r="C13">
-        <v>545.0274509999999</v>
+        <v>38.3610756</v>
       </c>
       <c r="D13">
-        <v>0.12706839999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>430.38810639999997</v>
+      </c>
+      <c r="E13">
+        <v>0.11749630000000003</v>
+      </c>
+      <c r="F13">
+        <v>77.13500000000009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13.0</v>
       </c>
       <c r="B14">
-        <v>3.471169582e9</v>
+        <v>2.091044392e9</v>
       </c>
       <c r="C14">
-        <v>535.4644764000001</v>
+        <v>37.6874435</v>
       </c>
       <c r="D14">
-        <v>0.17017619999999986</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>433.92937340000003</v>
+      </c>
+      <c r="E14">
+        <v>0.11767090000000015</v>
+      </c>
+      <c r="F14">
+        <v>77.67000000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14.0</v>
       </c>
       <c r="B15">
-        <v>3.884127673e9</v>
+        <v>8.31598479e8</v>
       </c>
       <c r="C15">
-        <v>513.8270001</v>
+        <v>39.023505899999996</v>
       </c>
       <c r="D15">
-        <v>0.1323898</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>433.1417591</v>
+      </c>
+      <c r="E15">
+        <v>0.10886610000000008</v>
+      </c>
+      <c r="F15">
+        <v>78.00500000000008</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15.0</v>
       </c>
       <c r="B16">
-        <v>2.040108525e9</v>
+        <v>9.87231325e8</v>
       </c>
       <c r="C16">
-        <v>473.52634459999996</v>
+        <v>38.7818244</v>
       </c>
       <c r="D16">
-        <v>0.13669749999999994</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>423.546117</v>
+      </c>
+      <c r="E16">
+        <v>0.1142729000000001</v>
+      </c>
+      <c r="F16">
+        <v>81.93000000000008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16.0</v>
       </c>
       <c r="B17">
-        <v>4.54653761e8</v>
+        <v>3.577420604e9</v>
       </c>
       <c r="C17">
-        <v>476.6180341</v>
+        <v>36.2487664</v>
       </c>
       <c r="D17">
-        <v>0.10969209999999993</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>413.99485350000003</v>
+      </c>
+      <c r="E17">
+        <v>0.10833490000000003</v>
+      </c>
+      <c r="F17">
+        <v>71.50500000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17.0</v>
       </c>
       <c r="B18">
-        <v>2.80609224e8</v>
+        <v>9.09005224e8</v>
       </c>
       <c r="C18">
-        <v>495.35705859999996</v>
+        <v>37.5349354</v>
       </c>
       <c r="D18">
-        <v>0.12017230000000005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>418.44682739999996</v>
+      </c>
+      <c r="E18">
+        <v>0.11858239999999988</v>
+      </c>
+      <c r="F18">
+        <v>88.71000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18.0</v>
       </c>
       <c r="B19">
-        <v>2.764309043e9</v>
+        <v>3.441992833e9</v>
       </c>
       <c r="C19">
-        <v>487.72683799999993</v>
+        <v>37.200595500000006</v>
       </c>
       <c r="D19">
-        <v>0.10988839999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>421.8670878</v>
+      </c>
+      <c r="E19">
+        <v>0.1150256999999999</v>
+      </c>
+      <c r="F19">
+        <v>75.59000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19.0</v>
       </c>
       <c r="B20">
-        <v>1.72438964e8</v>
+        <v>3.885064994e9</v>
       </c>
       <c r="C20">
-        <v>480.51335299999994</v>
+        <v>36.915528800000004</v>
       </c>
       <c r="D20">
-        <v>0.1068175999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>415.1426565</v>
+      </c>
+      <c r="E20">
+        <v>0.1281611</v>
+      </c>
+      <c r="F20">
+        <v>85.74500000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20.0</v>
       </c>
       <c r="B21">
-        <v>1.699171387e9</v>
+        <v>3.102434627e9</v>
       </c>
       <c r="C21">
-        <v>486.4307341</v>
+        <v>37.2900194</v>
       </c>
       <c r="D21">
-        <v>0.11856680000000007</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>415.97817499999996</v>
+      </c>
+      <c r="E21">
+        <v>0.10692420000000002</v>
+      </c>
+      <c r="F21">
+        <v>70.41500000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21.0</v>
       </c>
       <c r="B22">
-        <v>6.35638153e8</v>
+        <v>2.664147819e9</v>
       </c>
       <c r="C22">
-        <v>492.4435761</v>
+        <v>37.3254902</v>
       </c>
       <c r="D22">
-        <v>0.11661299999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>416.5958107</v>
+      </c>
+      <c r="E22">
+        <v>0.10802400000000002</v>
+      </c>
+      <c r="F22">
+        <v>75.30500000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22.0</v>
       </c>
       <c r="B23">
-        <v>4.083347034e9</v>
+        <v>3.36619706e9</v>
       </c>
       <c r="C23">
-        <v>484.2651927</v>
+        <v>36.5859229</v>
       </c>
       <c r="D23">
-        <v>0.1392789</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>415.3510654</v>
+      </c>
+      <c r="E23">
+        <v>0.1085515</v>
+      </c>
+      <c r="F23">
+        <v>86.43500000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23.0</v>
       </c>
       <c r="B24">
-        <v>8.77130837e8</v>
+        <v>4.165039328e9</v>
       </c>
       <c r="C24">
-        <v>486.5320661</v>
+        <v>37.6667336</v>
       </c>
       <c r="D24">
-        <v>0.12324400000000012</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>416.7521556</v>
+      </c>
+      <c r="E24">
+        <v>0.11502619999999998</v>
+      </c>
+      <c r="F24">
+        <v>79.12000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>24.0</v>
       </c>
       <c r="B25">
-        <v>8.35595131e8</v>
+        <v>2.28420501e8</v>
       </c>
       <c r="C25">
-        <v>474.92417150000006</v>
+        <v>37.408291899999995</v>
       </c>
       <c r="D25">
-        <v>0.11563360000000006</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>415.6497582</v>
+      </c>
+      <c r="E25">
+        <v>0.11434410000000007</v>
+      </c>
+      <c r="F25">
+        <v>70.98000000000008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>25.0</v>
       </c>
       <c r="B26">
-        <v>5.77547508e8</v>
+        <v>6.85292598e8</v>
       </c>
       <c r="C26">
-        <v>495.85845749999993</v>
+        <v>36.648554600000004</v>
       </c>
       <c r="D26">
-        <v>0.1188788000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>414.769188</v>
+      </c>
+      <c r="E26">
+        <v>0.13227129999999998</v>
+      </c>
+      <c r="F26">
+        <v>75.93000000000008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>26.0</v>
       </c>
       <c r="B27">
-        <v>2.998853969e9</v>
+        <v>1.485309619e9</v>
       </c>
       <c r="C27">
-        <v>474.2275382</v>
+        <v>37.561709300000004</v>
       </c>
       <c r="D27">
-        <v>0.1188099000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>416.44740740000003</v>
+      </c>
+      <c r="E27">
+        <v>0.12123510000000004</v>
+      </c>
+      <c r="F27">
+        <v>76.48000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>27.0</v>
       </c>
       <c r="B28">
-        <v>1.586751529e9</v>
+        <v>2.096891469e9</v>
       </c>
       <c r="C28">
-        <v>474.3333233</v>
+        <v>37.5950913</v>
       </c>
       <c r="D28">
-        <v>0.11042359999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>417.8411215</v>
+      </c>
+      <c r="E28">
+        <v>0.1169917000000001</v>
+      </c>
+      <c r="F28">
+        <v>81.25500000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>28.0</v>
       </c>
       <c r="B29">
-        <v>1.29425463e9</v>
+        <v>2.777849021e9</v>
       </c>
       <c r="C29">
-        <v>488.1686515</v>
+        <v>38.0256217</v>
       </c>
       <c r="D29">
-        <v>0.11050820000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>415.77167910000003</v>
+      </c>
+      <c r="E29">
+        <v>0.10835179999999994</v>
+      </c>
+      <c r="F29">
+        <v>78.03000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>29.0</v>
       </c>
       <c r="B30">
-        <v>1.3386224e7</v>
+        <v>4.079851142e9</v>
       </c>
       <c r="C30">
-        <v>474.1778383</v>
+        <v>37.4249206</v>
       </c>
       <c r="D30">
-        <v>0.11140479999999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>415.35712789999997</v>
+      </c>
+      <c r="E30">
+        <v>0.1218267</v>
+      </c>
+      <c r="F30">
+        <v>79.40500000000007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>30.0</v>
       </c>
       <c r="B31">
-        <v>2.08488696e8</v>
+        <v>1.845944302e9</v>
       </c>
       <c r="C31">
-        <v>473.2513776</v>
+        <v>37.2903523</v>
       </c>
       <c r="D31">
-        <v>0.10882139999999992</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>416.470422</v>
+      </c>
+      <c r="E31">
+        <v>0.11480880000000003</v>
+      </c>
+      <c r="F31">
+        <v>80.77000000000007</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>31.0</v>
       </c>
       <c r="B32">
-        <v>3.604894635e9</v>
+        <v>3.102449918e9</v>
       </c>
       <c r="C32">
-        <v>474.4228328</v>
+        <v>36.412491100000004</v>
       </c>
       <c r="D32">
-        <v>0.10686780000000005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>415.7041844</v>
+      </c>
+      <c r="E32">
+        <v>0.1167954999999999</v>
+      </c>
+      <c r="F32">
+        <v>87.8650000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>32.0</v>
       </c>
       <c r="B33">
-        <v>2.880005102e9</v>
+        <v>1.02295728e9</v>
       </c>
       <c r="C33">
-        <v>473.9567574</v>
+        <v>37.6128541</v>
       </c>
       <c r="D33">
-        <v>0.11804210000000008</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>415.3982535</v>
+      </c>
+      <c r="E33">
+        <v>0.1149211</v>
+      </c>
+      <c r="F33">
+        <v>79.48000000000009</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>33.0</v>
       </c>
       <c r="B34">
-        <v>5.28613462e8</v>
+        <v>2.960937514e9</v>
       </c>
       <c r="C34">
-        <v>474.2280843</v>
+        <v>37.353251300000004</v>
       </c>
       <c r="D34">
-        <v>0.11724499999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>415.44712310000006</v>
+      </c>
+      <c r="E34">
+        <v>0.11592370000000006</v>
+      </c>
+      <c r="F34">
+        <v>80.18500000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>34.0</v>
       </c>
       <c r="B35">
-        <v>2.3304539e7</v>
+        <v>4.34164195e8</v>
       </c>
       <c r="C35">
-        <v>472.8061336</v>
+        <v>36.561210499999994</v>
       </c>
       <c r="D35">
-        <v>0.11623510000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>414.6216252</v>
+      </c>
+      <c r="E35">
+        <v>0.11010389999999992</v>
+      </c>
+      <c r="F35">
+        <v>85.81500000000007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>35.0</v>
       </c>
       <c r="B36">
-        <v>2.366350622e9</v>
+        <v>4.239228961e9</v>
       </c>
       <c r="C36">
-        <v>473.24297029999997</v>
+        <v>37.5094917</v>
       </c>
       <c r="D36">
-        <v>0.12057690000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>415.64054899999996</v>
+      </c>
+      <c r="E36">
+        <v>0.12990600000000002</v>
+      </c>
+      <c r="F36">
+        <v>83.42000000000009</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>36.0</v>
       </c>
       <c r="B37">
-        <v>6.36730993e8</v>
+        <v>1.573602106e9</v>
       </c>
       <c r="C37">
-        <v>472.80572170000005</v>
+        <v>37.4241673</v>
       </c>
       <c r="D37">
-        <v>0.10744510000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>416.3995075</v>
+      </c>
+      <c r="E37">
+        <v>0.11396550000000004</v>
+      </c>
+      <c r="F37">
+        <v>84.55000000000007</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>37.0</v>
       </c>
       <c r="B38">
-        <v>2.20794944e8</v>
+        <v>4.1793608e7</v>
       </c>
       <c r="C38">
-        <v>475.2145293</v>
+        <v>36.4519446</v>
       </c>
       <c r="D38">
-        <v>0.12370639999999991</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>415.16814669999997</v>
+      </c>
+      <c r="E38">
+        <v>0.12430249999999983</v>
+      </c>
+      <c r="F38">
+        <v>76.53500000000005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>38.0</v>
       </c>
       <c r="B39">
-        <v>7.80636322e8</v>
+        <v>3.972672008e9</v>
       </c>
       <c r="C39">
-        <v>473.69427340000004</v>
+        <v>37.484812100000006</v>
       </c>
       <c r="D39">
-        <v>0.1083612</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>414.47398089999996</v>
+      </c>
+      <c r="E39">
+        <v>0.11516769999999997</v>
+      </c>
+      <c r="F39">
+        <v>77.62500000000007</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>39.0</v>
       </c>
       <c r="B40">
-        <v>1.21764727e9</v>
+        <v>2.123260612e9</v>
       </c>
       <c r="C40">
-        <v>473.30803829999996</v>
+        <v>37.2576504</v>
       </c>
       <c r="D40">
-        <v>0.10689640000000014</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>416.9632709</v>
+      </c>
+      <c r="E40">
+        <v>0.12524669999999982</v>
+      </c>
+      <c r="F40">
+        <v>72.57000000000006</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>40.0</v>
       </c>
       <c r="B41">
-        <v>5.41034342e8</v>
+        <v>4.099719556e9</v>
       </c>
       <c r="C41">
-        <v>473.9591313</v>
+        <v>36.625815599999996</v>
       </c>
       <c r="D41">
-        <v>0.13781370000000004</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>415.6681582</v>
+      </c>
+      <c r="E41">
+        <v>0.11164229999999996</v>
+      </c>
+      <c r="F41">
+        <v>86.92000000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>41.0</v>
       </c>
       <c r="B42">
-        <v>6.24355488e8</v>
+        <v>4.159095108e9</v>
       </c>
       <c r="C42">
-        <v>472.6217108000001</v>
+        <v>37.588642</v>
       </c>
       <c r="D42">
-        <v>0.1161278</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>415.9450451</v>
+      </c>
+      <c r="E42">
+        <v>0.1168384</v>
+      </c>
+      <c r="F42">
+        <v>73.73500000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>42.0</v>
       </c>
       <c r="B43">
-        <v>2.957468453e9</v>
+        <v>1.918660258e9</v>
       </c>
       <c r="C43">
-        <v>471.7952039</v>
+        <v>37.344608799999996</v>
       </c>
       <c r="D43">
-        <v>0.12317760000000004</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>417.2890281</v>
+      </c>
+      <c r="E43">
+        <v>0.10856109999999998</v>
+      </c>
+      <c r="F43">
+        <v>69.72500000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>43.0</v>
       </c>
       <c r="B44">
-        <v>2.202415316e9</v>
+        <v>2.336429712e9</v>
       </c>
       <c r="C44">
-        <v>474.5988412</v>
+        <v>36.414236200000005</v>
       </c>
       <c r="D44">
-        <v>0.12472270000000008</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>492.7940837</v>
+      </c>
+      <c r="E44">
+        <v>0.16354559999999987</v>
+      </c>
+      <c r="F44">
+        <v>67.91500000000006</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>44.0</v>
       </c>
       <c r="B45">
-        <v>3.728329132e9</v>
+        <v>2.396820561e9</v>
       </c>
       <c r="C45">
-        <v>474.3710965</v>
+        <v>42.3513831</v>
       </c>
       <c r="D45">
-        <v>0.13624419999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>479.63919699999997</v>
+      </c>
+      <c r="E45">
+        <v>0.12116000000000003</v>
+      </c>
+      <c r="F45">
+        <v>72.69000000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>45.0</v>
       </c>
       <c r="B46">
-        <v>8.08794169e8</v>
+        <v>1.126232703e9</v>
       </c>
       <c r="C46">
-        <v>475.1840104</v>
+        <v>39.4768288</v>
       </c>
       <c r="D46">
-        <v>0.1250966999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>463.07459409999996</v>
+      </c>
+      <c r="E46">
+        <v>0.16108009999999992</v>
+      </c>
+      <c r="F46">
+        <v>83.74500000000006</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>46.0</v>
       </c>
       <c r="B47">
-        <v>1.159787155e9</v>
+        <v>1.797426574e9</v>
       </c>
       <c r="C47">
-        <v>472.61202890000004</v>
+        <v>43.7883867</v>
       </c>
       <c r="D47">
-        <v>0.12354630000000005</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>460.8474127999999</v>
+      </c>
+      <c r="E47">
+        <v>0.12209409999999993</v>
+      </c>
+      <c r="F47">
+        <v>82.93500000000006</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>47.0</v>
       </c>
       <c r="B48">
-        <v>2.272248243e9</v>
+        <v>6.96851988e8</v>
       </c>
       <c r="C48">
-        <v>473.86591059999995</v>
+        <v>47.1814188</v>
       </c>
       <c r="D48">
-        <v>0.12407820000000008</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>465.02357130000007</v>
+      </c>
+      <c r="E48">
+        <v>0.11157049999999992</v>
+      </c>
+      <c r="F48">
+        <v>80.52000000000004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>48.0</v>
       </c>
       <c r="B49">
-        <v>8.6596016e7</v>
+        <v>1.669123377e9</v>
       </c>
       <c r="C49">
-        <v>473.4451983</v>
+        <v>39.2382051</v>
       </c>
       <c r="D49">
-        <v>0.1178871999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>471.0518479</v>
+      </c>
+      <c r="E49">
+        <v>0.13276929999999998</v>
+      </c>
+      <c r="F49">
+        <v>71.38500000000006</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>49.0</v>
       </c>
       <c r="B50">
-        <v>1.180254309e9</v>
+        <v>4.170008386e9</v>
       </c>
       <c r="C50">
-        <v>474.1713368</v>
+        <v>39.9759989</v>
       </c>
       <c r="D50">
-        <v>0.10869200000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>455.9322173</v>
+      </c>
+      <c r="E50">
+        <v>0.11330120000000002</v>
+      </c>
+      <c r="F50">
+        <v>79.41000000000007</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>50.0</v>
       </c>
       <c r="B51">
-        <v>4.106517475e9</v>
+        <v>1.933531244e9</v>
       </c>
       <c r="C51">
-        <v>472.936771</v>
+        <v>45.9778769</v>
       </c>
       <c r="D51">
-        <v>0.1140172</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>472.6228124</v>
+      </c>
+      <c r="E51">
+        <v>0.11695189999999993</v>
+      </c>
+      <c r="F51">
+        <v>76.09000000000007</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B53">
-        <v>497.893601556</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>38.187105628</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B54">
-        <v>0.15086934600000007</v>
+        <v>427.54704379200007</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55">
+        <v>465.73414942000005</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56">
+        <v>0.14348473</v>
       </c>
     </row>
   </sheetData>
